--- a/xlsx/Power/p12.xlsx
+++ b/xlsx/Power/p12.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\36306\Desktop\ERFP_SzilardPalma\Normality test\ReplicationCode\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBC6D104-7257-4E2E-8DF3-B375BB8F6CC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6EE20CA-79C0-4762-A6A6-0B4C48467F56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3420" yWindow="3420" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{55F207A2-7B4F-436C-BC53-89FA13857D3F}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{55F207A2-7B4F-436C-BC53-89FA13857D3F}"/>
   </bookViews>
   <sheets>
     <sheet name="Munka1" sheetId="1" r:id="rId1"/>
@@ -436,7 +436,7 @@
         <v>0.999</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>0.999</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -494,7 +494,7 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>0.89</v>
+        <v>0.90100000000000002</v>
       </c>
       <c r="B4">
         <v>0.995</v>
@@ -596,7 +596,7 @@
         <v>0.97</v>
       </c>
       <c r="C7">
-        <v>0.997</v>
+        <v>0.996</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -628,7 +628,7 @@
         <v>0.999</v>
       </c>
       <c r="C8">
-        <v>1</v>
+        <v>0.98799999999999999</v>
       </c>
       <c r="D8">
         <v>1</v>
@@ -660,19 +660,19 @@
         <v>0.94499999999999995</v>
       </c>
       <c r="C9">
-        <v>0.95499999999999996</v>
+        <v>0.996</v>
       </c>
       <c r="D9">
-        <v>0.93899999999999995</v>
+        <v>1</v>
       </c>
       <c r="E9">
-        <v>0.96499999999999997</v>
+        <v>1</v>
       </c>
       <c r="F9">
-        <v>0.98399999999999999</v>
+        <v>0.999</v>
       </c>
       <c r="G9">
-        <v>0.998</v>
+        <v>0.999</v>
       </c>
       <c r="H9">
         <v>1</v>

--- a/xlsx/Power/p12.xlsx
+++ b/xlsx/Power/p12.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\36306\Desktop\ERFP_SzilardPalma\Normality test\ReplicationCode\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6EE20CA-79C0-4762-A6A6-0B4C48467F56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2071BD3-657D-46F4-A72D-AA071E992BDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{55F207A2-7B4F-436C-BC53-89FA13857D3F}"/>
+    <workbookView xWindow="3510" yWindow="3510" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{55F207A2-7B4F-436C-BC53-89FA13857D3F}"/>
   </bookViews>
   <sheets>
     <sheet name="Munka1" sheetId="1" r:id="rId1"/>
@@ -436,7 +436,7 @@
         <v>0.999</v>
       </c>
       <c r="C2">
-        <v>0.999</v>
+        <v>1</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -494,7 +494,7 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>0.90100000000000002</v>
+        <v>0.89</v>
       </c>
       <c r="B4">
         <v>0.995</v>
@@ -596,7 +596,7 @@
         <v>0.97</v>
       </c>
       <c r="C7">
-        <v>0.996</v>
+        <v>0.997</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -628,7 +628,7 @@
         <v>0.999</v>
       </c>
       <c r="C8">
-        <v>0.98799999999999999</v>
+        <v>1</v>
       </c>
       <c r="D8">
         <v>1</v>
@@ -660,19 +660,19 @@
         <v>0.94499999999999995</v>
       </c>
       <c r="C9">
-        <v>0.996</v>
+        <v>0.95499999999999996</v>
       </c>
       <c r="D9">
-        <v>1</v>
+        <v>0.93899999999999995</v>
       </c>
       <c r="E9">
-        <v>1</v>
+        <v>0.96499999999999997</v>
       </c>
       <c r="F9">
-        <v>0.999</v>
+        <v>0.98399999999999999</v>
       </c>
       <c r="G9">
-        <v>0.999</v>
+        <v>0.998</v>
       </c>
       <c r="H9">
         <v>1</v>

--- a/xlsx/Power/p12.xlsx
+++ b/xlsx/Power/p12.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\36306\Desktop\ERFP_SzilardPalma\Normality test\ReplicationCode\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2071BD3-657D-46F4-A72D-AA071E992BDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECEDDFD6-981C-4F50-91C8-2652AECEE6EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3510" yWindow="3510" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{55F207A2-7B4F-436C-BC53-89FA13857D3F}"/>
+    <workbookView xWindow="1950" yWindow="1950" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{55F207A2-7B4F-436C-BC53-89FA13857D3F}"/>
   </bookViews>
   <sheets>
     <sheet name="Munka1" sheetId="1" r:id="rId1"/>
@@ -430,7 +430,7 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>0.91</v>
+        <v>0.90800000000000003</v>
       </c>
       <c r="B2">
         <v>0.999</v>
@@ -462,7 +462,7 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>0.90300000000000002</v>
+        <v>0.90200000000000002</v>
       </c>
       <c r="B3">
         <v>0.998</v>
@@ -494,7 +494,7 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>0.89</v>
+        <v>0.88700000000000001</v>
       </c>
       <c r="B4">
         <v>0.995</v>
@@ -526,16 +526,16 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>1</v>
+        <v>0.22800000000000001</v>
       </c>
       <c r="B5">
-        <v>1</v>
+        <v>0.76700000000000002</v>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>0.96599999999999997</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>0.997</v>
       </c>
       <c r="E5">
         <v>1</v>
@@ -558,7 +558,7 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>0.81499999999999995</v>
+        <v>0.80900000000000005</v>
       </c>
       <c r="B6">
         <v>0.98099999999999998</v>
@@ -590,13 +590,13 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>0.77200000000000002</v>
+        <v>0.77</v>
       </c>
       <c r="B7">
         <v>0.97</v>
       </c>
       <c r="C7">
-        <v>0.997</v>
+        <v>0.996</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -657,19 +657,19 @@
         <v>0.71399999999999997</v>
       </c>
       <c r="B9">
-        <v>0.94499999999999995</v>
+        <v>0.94599999999999995</v>
       </c>
       <c r="C9">
         <v>0.95499999999999996</v>
       </c>
       <c r="D9">
-        <v>0.93899999999999995</v>
+        <v>0.94</v>
       </c>
       <c r="E9">
-        <v>0.96499999999999997</v>
+        <v>0.96299999999999997</v>
       </c>
       <c r="F9">
-        <v>0.98399999999999999</v>
+        <v>0.98499999999999999</v>
       </c>
       <c r="G9">
         <v>0.998</v>
